--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/nov-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/nov-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1182.56</v>
+        <v>1172.55</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>568.23</v>
+        <v>563.42</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9532.280000000001</v>
+        <v>9451.549999999999</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>734.5</v>
+        <v>728.28</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8150.11</v>
+        <v>8081.08</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6364.48</v>
+        <v>6310.57</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1161.01</v>
+        <v>1151.17</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>449.29</v>
+        <v>446.98</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11090.8</v>
+        <v>11033.82</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7485.81</v>
+        <v>7447.34</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>449.29</v>
+        <v>446.98</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8150.11</v>
+        <v>8108.23</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2502.55</v>
+        <v>2489.7</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8138.94</v>
+        <v>8097.12</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>9279.959999999999</v>
+        <v>9232.280000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>449.29</v>
+        <v>446.98</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8761.360000000001</v>
+        <v>8716.34</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>635.99</v>
+        <v>632.73</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>397.28</v>
+        <v>395.24</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9266.17</v>
+        <v>9218.559999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>343.09</v>
+        <v>341.32</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8627.27</v>
+        <v>8541.17</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1927.66</v>
+        <v>1908.42</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8941.57</v>
+        <v>8852.33</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>36317.29</v>
+        <v>35954.84</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>8150.11</v>
+        <v>8068.77</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8627.27</v>
+        <v>8541.17</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>449.29</v>
+        <v>444.81</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>9372.620000000001</v>
+        <v>9279.08</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>36741.68</v>
+        <v>36375</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>257.37</v>
+        <v>254.81</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8150.11</v>
+        <v>8064.76</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>25181.22</v>
+        <v>24917.51</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>14950.77</v>
+        <v>14794.2</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>687.17</v>
+        <v>679.97</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>122.41</v>
+        <v>121.13</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>555.6900000000001</v>
+        <v>549.87</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>378.99</v>
+        <v>375.02</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7320.25</v>
+        <v>7243.6</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8069.53</v>
+        <v>7985.03</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5144.98</v>
+        <v>5091.1</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>17855.39</v>
+        <v>17668.4</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>9290.09</v>
+        <v>9192.809999999999</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>11317.5</v>
+        <v>11255.64</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8610.610000000001</v>
+        <v>8563.540000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>14259.62</v>
+        <v>14181.68</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>9719.74</v>
+        <v>9666.610000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>449.29</v>
+        <v>446.83</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>909.22</v>
+        <v>904.25</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>541.67</v>
+        <v>538.71</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1954.31</v>
+        <v>1943.63</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>651.91</v>
+        <v>648.35</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>8069.53</v>
+        <v>8025.43</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8610.610000000001</v>
+        <v>8563.540000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>606.61</v>
+        <v>603.3</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2183.99</v>
+        <v>2172.05</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>25575.32</v>
+        <v>25435.53</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8946.98</v>
+        <v>8847.299999999999</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>489.99</v>
+        <v>484.53</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>9372.620000000001</v>
+        <v>9268.200000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>757.92</v>
+        <v>749.48</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>764.34</v>
+        <v>755.8200000000001</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>6924.83</v>
+        <v>6847.68</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>806.11</v>
+        <v>797.13</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>488.52</v>
+        <v>483.08</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1363.6</v>
+        <v>1348.41</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3429.99</v>
+        <v>3391.77</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>8150.11</v>
+        <v>8059.3</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>449.29</v>
+        <v>444.28</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3233.75</v>
+        <v>3216.04</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>19631.53</v>
+        <v>19524.02</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>8054.81</v>
+        <v>8044.56</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4612.95</v>
+        <v>4607.08</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2667.92</v>
+        <v>2664.53</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>4629.15</v>
+        <v>4645.67</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>10732.5</v>
+        <v>10770.8</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>7232.69</v>
+        <v>7258.51</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>559.23</v>
+        <v>565.3099999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>8557.610000000001</v>
+        <v>8650.690000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>570.71</v>
+        <v>576.92</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>258.62</v>
+        <v>261.44</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>8816.219999999999</v>
+        <v>8912.110000000001</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2696.17</v>
+        <v>2725.5</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5676.23</v>
+        <v>5737.96</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>9072.35</v>
+        <v>9102.190000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>490.47</v>
+        <v>492.08</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>8557.610000000001</v>
+        <v>8585.76</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>35941.1</v>
+        <v>36059.31</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>9047.540000000001</v>
+        <v>9077.299999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>998.0700000000001</v>
+        <v>1001.36</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>449.29</v>
+        <v>450.77</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>18095.08</v>
+        <v>18154.59</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>8150.11</v>
+        <v>8176.91</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>959.59</v>
+        <v>962.75</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8557.610000000001</v>
+        <v>8585.76</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>449.29</v>
+        <v>450.77</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>14837.84</v>
+        <v>15093.96</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>7906.65</v>
+        <v>8043.13</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>8138.94</v>
+        <v>8279.43</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2366.53</v>
+        <v>2377.56</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>449.29</v>
+        <v>451.38</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8610.610000000001</v>
+        <v>8650.709999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>584.64</v>
+        <v>587.36</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>449.29</v>
+        <v>451.38</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>18250.02</v>
+        <v>18335.02</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>8558.51</v>
+        <v>8598.370000000001</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3431.57</v>
+        <v>3447.55</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>570.71</v>
+        <v>573.37</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>4834.03</v>
+        <v>4856.54</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>527.45</v>
+        <v>529.9</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>8610.610000000001</v>
+        <v>8672.690000000001</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3479.04</v>
+        <v>3504.12</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>10334.4</v>
+        <v>10408.91</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>10621.89</v>
+        <v>10698.47</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>571.62</v>
+        <v>575.74</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>8610.610000000001</v>
+        <v>8672.690000000001</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>641.98</v>
+        <v>646.61</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1802.52</v>
+        <v>1815.51</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>8627.450000000001</v>
+        <v>8689.65</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2065.02</v>
+        <v>2079.91</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>449.29</v>
+        <v>452.53</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>24487.08</v>
+        <v>24443.65</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>511.73</v>
+        <v>510.82</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>449.29</v>
+        <v>448.49</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>9279.959999999999</v>
+        <v>9263.51</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1046.39</v>
+        <v>1044.53</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>9372.620000000001</v>
+        <v>9356</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>449.29</v>
+        <v>448.49</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>441.4</v>
+        <v>440.62</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>8057.54</v>
+        <v>8043.25</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>126.66</v>
+        <v>126.44</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>8150.97</v>
+        <v>8136.51</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>449.29</v>
+        <v>447.44</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>8610.610000000001</v>
+        <v>8575.120000000001</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>9372.620000000001</v>
+        <v>9333.99</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>740.71</v>
+        <v>737.65</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>449.29</v>
+        <v>447.44</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>449.29</v>
+        <v>447.44</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>8557.610000000001</v>
+        <v>8522.34</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>8557.610000000001</v>
+        <v>8522.34</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>9372.620000000001</v>
+        <v>9333.99</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1006.56</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2065.37</v>
+        <v>2062.17</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>163.25</v>
+        <v>163</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>36855.52</v>
+        <v>36798.4</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>449.29</v>
+        <v>448.59</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>449.29</v>
+        <v>448.59</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>8761.1</v>
+        <v>8747.52</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2532.23</v>
+        <v>2528.31</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3840.79</v>
+        <v>3834.84</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>8761.1</v>
+        <v>8747.52</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>3985.13</v>
+        <v>4005.71</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>449.29</v>
+        <v>451.61</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>667.3099999999999</v>
+        <v>670.76</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>8150.11</v>
+        <v>8192.200000000001</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>449.29</v>
+        <v>451.61</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>449.29</v>
+        <v>451.61</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>449.29</v>
+        <v>451.61</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>898.58</v>
+        <v>903.22</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3573.27</v>
+        <v>3591.72</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>109.94</v>
+        <v>110.51</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>8558.51</v>
+        <v>8618.92</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2078.09</v>
+        <v>2092.75</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>9372.620000000001</v>
+        <v>9438.77</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>449.29</v>
+        <v>452.46</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>8558.51</v>
+        <v>8618.92</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>8150.11</v>
+        <v>8207.629999999999</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>449.29</v>
+        <v>452.46</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>8138.94</v>
+        <v>8196.379999999999</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>6213.99</v>
+        <v>6257.85</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>10982.7</v>
+        <v>11060.21</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>9279.959999999999</v>
+        <v>9345.459999999999</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>671.98</v>
+        <v>676.72</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>10621.84</v>
+        <v>10696.81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/nov-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/nov-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1172.55</v>
+        <v>1176.44</v>
       </c>
     </row>
     <row r="3">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/nov-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/nov-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/nov-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/nov-2025.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Comandancia en Jefe de la IV Zona Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/nov-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/nov-2025.xlsx
@@ -562,7 +562,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1127,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1192,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1501,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1627,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1692,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1757,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1822,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1948,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2013,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2078,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2265,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2391,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2700,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2765,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2830,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2895,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3143,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3452,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3517,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3704,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3769,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3956,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4021,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4086,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4212,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4338,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4403,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4468,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4533,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4842,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5029,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5094,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5159,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5224,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5289,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5354,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5419,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5606,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5732,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5797,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5923,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6049,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6175,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6240,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6427,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6553,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6618,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6683,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6809,11 @@
           <t>77.814.662-2</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6874,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7061,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7126,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7191,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7378,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7443,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7569,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7634,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7699,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7764,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8134,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8199,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8264,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8329,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8455,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8581,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8646,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8894,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9081,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9146,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9211,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9520,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9585,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9650,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9715,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9780,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10089,11 @@
           <t>77.820.166-6</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10154,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10341,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10406,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10471,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10536,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10662,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10727,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10914,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10979,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11105,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11231,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11296,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
